--- a/Протоколы/lab1.xlsx
+++ b/Протоколы/lab1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\study\works\Протоколы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\Протоколы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF2E567-EEEB-4115-B044-59C2D60EAD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3D3A5-2E38-4EE8-BAE9-3466BC75942A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="2265" windowWidth="16080" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Системные требования</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>Download:90 Upload:  77</t>
+  </si>
+  <si>
+    <t>ip.src</t>
+  </si>
+  <si>
+    <t>ip.dst</t>
   </si>
 </sst>
 </file>
@@ -420,14 +426,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="6" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="6" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
@@ -435,7 +441,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -446,7 +452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -457,7 +463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -468,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -478,8 +484,11 @@
       <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -489,8 +498,11 @@
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
